--- a/mlef_pipeline/results/OS_24/IO_ONLY/RWD/results.xlsx
+++ b/mlef_pipeline/results/OS_24/IO_ONLY/RWD/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.69 ± 0.04</t>
+          <t>0.70 ± 0.04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.59 ± 0.03</t>
+          <t>0.60 ± 0.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.61 ± 0.07</t>
+          <t>0.62 ± 0.07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.65 ± 0.09</t>
+          <t>0.66 ± 0.10</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.69 ± 0.10</t>
+          <t>0.70 ± 0.10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
